--- a/肝病报告生成-对比实验.xlsx
+++ b/肝病报告生成-对比实验.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Method</t>
   </si>
@@ -112,13 +112,16 @@
     <t>MRI2Rep: Autoregressive Structured Report Generation for 3D Liver MRI</t>
   </si>
   <si>
+    <t>Merlin: a computed tomography vision-language foundation model and dataset</t>
+  </si>
+  <si>
+    <t>(zero-shot)</t>
+  </si>
+  <si>
     <t>Astra</t>
   </si>
   <si>
     <t>Astra: a generalizable report generation foundation model for 3D computed tomography</t>
-  </si>
-  <si>
-    <t>(zero-shot)</t>
   </si>
 </sst>
 </file>
@@ -1162,8 +1165,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15"/>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1" customWidth="1"/>
     <col min="2" max="8" width="10.125" style="2" customWidth="1"/>
@@ -1171,7 +1174,7 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
+    <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" customHeight="1" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1238,7 +1241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" customHeight="1" spans="1:9">
       <c r="A10" s="11" t="s">
         <v>18</v>
       </c>
@@ -1265,125 +1268,142 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" customHeight="1" spans="1:9">
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" ht="15.75" spans="1:9">
-      <c r="A13" s="15" t="s">
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" ht="15.75"/>
-    <row r="22" spans="6:10">
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="6:10">
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="6:10">
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="24" customHeight="1" spans="6:10">
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="6:10">
+    <row r="25" customHeight="1" spans="6:10">
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="6:10">
+    <row r="26" customHeight="1" spans="6:10">
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="6:10">
+    <row r="27" customHeight="1" spans="6:10">
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="6:10">
+    <row r="28" customHeight="1" spans="6:10">
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="6:10">
+    <row r="29" customHeight="1" spans="6:10">
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="6:10">
+    <row r="30" customHeight="1" spans="6:10">
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="20"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="6:10">
+    <row r="31" customHeight="1" spans="6:10">
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="6:10">
+    <row r="32" customHeight="1" spans="6:10">
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="20"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="6:10">
+    <row r="33" customHeight="1" spans="6:10">
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
       <c r="I33" s="20"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="6:10">
+    <row r="34" customHeight="1" spans="6:10">
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
+    </row>
+    <row r="35" customHeight="1" spans="6:10">
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" customHeight="1" spans="6:10">
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1392,7 +1412,8 @@
     <hyperlink ref="I8" r:id="rId3" display="Towards generalist foundation model for radiology by leveraging web-scale 2D&amp;3D medical data"/>
     <hyperlink ref="I2" r:id="rId4" display="M3D: Advancing 3D Medical Image Analysis with Multi-Modal Large Language Models"/>
     <hyperlink ref="I10" r:id="rId5" display="MRI2Rep: Autoregressive Structured Report Generation for 3D Liver MRI"/>
-    <hyperlink ref="I12" r:id="rId6" display="Astra: a generalizable report generation foundation model for 3D computed tomography"/>
+    <hyperlink ref="I14" r:id="rId6" display="Astra: a generalizable report generation foundation model for 3D computed tomography"/>
+    <hyperlink ref="I12" r:id="rId7" display="Merlin: a computed tomography vision-language foundation model and dataset"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/肝病报告生成-对比实验.xlsx
+++ b/肝病报告生成-对比实验.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Method</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>LLM-Eval ↑</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <r>
@@ -80,6 +83,27 @@
     <t>CT2Rep</t>
   </si>
   <si>
+    <t>测试生成文本完全一致，模型输出频次最高模板。</t>
+  </si>
+  <si>
+    <t>CT2Rep: Automated Radiology Report Generation for 3D Medical Imaging</t>
+  </si>
+  <si>
+    <t>Merlin</t>
+  </si>
+  <si>
+    <t>Merlin: a computed tomography vision–language foundation model and dataset</t>
+  </si>
+  <si>
+    <t>RadFM</t>
+  </si>
+  <si>
+    <t>Towards generalist foundation model for radiology by leveraging web-scale 2D&amp;3D medical data</t>
+  </si>
+  <si>
+    <t>MRI2Rep</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -89,24 +113,6 @@
       </rPr>
       <t>正在复现</t>
     </r>
-  </si>
-  <si>
-    <t>CT2Rep: Automated Radiology Report Generation for 3D Medical Imaging</t>
-  </si>
-  <si>
-    <t>Merlin</t>
-  </si>
-  <si>
-    <t>Merlin: a computed tomography vision–language foundation model and dataset</t>
-  </si>
-  <si>
-    <t>RadFM</t>
-  </si>
-  <si>
-    <t>Towards generalist foundation model for radiology by leveraging web-scale 2D&amp;3D medical data</t>
-  </si>
-  <si>
-    <t>MRI2Rep</t>
   </si>
   <si>
     <t>MRI2Rep: Autoregressive Structured Report Generation for 3D Liver MRI</t>
@@ -134,7 +140,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +155,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -160,6 +172,11 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="0"/>
     </font>
     <font>
@@ -305,12 +322,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -660,137 +671,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -806,22 +817,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -830,10 +847,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,10 +859,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1165,16 +1182,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1" customWidth="1"/>
     <col min="2" max="8" width="10.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="88.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="41.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="88.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:9">
+    <row r="1" customHeight="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1199,221 +1217,255 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:10">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10" t="s">
+      <c r="B4" s="2">
+        <v>0.6217</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.5637</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.6718</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
+      <c r="J4" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="11" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="s">
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
+      <c r="B10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:9">
+        <v>15</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="A15" s="17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:10">
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" customHeight="1" spans="6:10">
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:10">
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:10">
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:10">
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:10">
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:10">
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:10">
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:10">
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:10">
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:10">
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" customHeight="1" spans="6:10">
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36" customHeight="1" spans="6:10">
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="24" customHeight="1" spans="6:11">
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+    </row>
+    <row r="25" customHeight="1" spans="6:11">
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:11">
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:11">
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:11">
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:11">
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+    </row>
+    <row r="30" customHeight="1" spans="6:11">
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:11">
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:11">
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+    </row>
+    <row r="33" customHeight="1" spans="6:11">
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+    </row>
+    <row r="34" customHeight="1" spans="6:11">
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+    </row>
+    <row r="35" customHeight="1" spans="6:11">
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+    </row>
+    <row r="36" customHeight="1" spans="6:11">
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" display="CT2Rep: Automated Radiology Report Generation for 3D Medical Imaging"/>
-    <hyperlink ref="I6" r:id="rId2" display="Merlin: a computed tomography vision–language foundation model and dataset"/>
-    <hyperlink ref="I8" r:id="rId3" display="Towards generalist foundation model for radiology by leveraging web-scale 2D&amp;3D medical data"/>
-    <hyperlink ref="I2" r:id="rId4" display="M3D: Advancing 3D Medical Image Analysis with Multi-Modal Large Language Models"/>
-    <hyperlink ref="I10" r:id="rId5" display="MRI2Rep: Autoregressive Structured Report Generation for 3D Liver MRI"/>
-    <hyperlink ref="I14" r:id="rId6" display="Astra: a generalizable report generation foundation model for 3D computed tomography"/>
-    <hyperlink ref="I12" r:id="rId7" display="Merlin: a computed tomography vision-language foundation model and dataset"/>
+    <hyperlink ref="J4" r:id="rId1" display="CT2Rep: Automated Radiology Report Generation for 3D Medical Imaging"/>
+    <hyperlink ref="J6" r:id="rId2" display="Merlin: a computed tomography vision–language foundation model and dataset"/>
+    <hyperlink ref="J8" r:id="rId3" display="Towards generalist foundation model for radiology by leveraging web-scale 2D&amp;3D medical data"/>
+    <hyperlink ref="J2" r:id="rId4" display="M3D: Advancing 3D Medical Image Analysis with Multi-Modal Large Language Models"/>
+    <hyperlink ref="J10" r:id="rId5" display="MRI2Rep: Autoregressive Structured Report Generation for 3D Liver MRI"/>
+    <hyperlink ref="J14" r:id="rId6" display="Astra: a generalizable report generation foundation model for 3D computed tomography"/>
+    <hyperlink ref="J12" r:id="rId7" display="Merlin: a computed tomography vision-language foundation model and dataset"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/肝病报告生成-对比实验.xlsx
+++ b/肝病报告生成-对比实验.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Method</t>
   </si>
@@ -121,13 +121,13 @@
     <t>Merlin: a computed tomography vision-language foundation model and dataset</t>
   </si>
   <si>
+    <t>Astra</t>
+  </si>
+  <si>
+    <t>Astra: a generalizable report generation foundation model for 3D computed tomography</t>
+  </si>
+  <si>
     <t>(zero-shot)</t>
-  </si>
-  <si>
-    <t>Astra</t>
-  </si>
-  <si>
-    <t>Astra: a generalizable report generation foundation model for 3D computed tomography</t>
   </si>
 </sst>
 </file>
@@ -1320,9 +1320,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="13" t="s">
-        <v>23</v>
-      </c>
+      <c r="A13" s="13"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="12"/>
@@ -1330,18 +1328,18 @@
     </row>
     <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
